--- a/data/trans_orig/IP04F-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP04F-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76996</t>
+          <t>77284</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86896</t>
+          <t>86769</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75004</t>
+          <t>75338</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83561</t>
+          <t>83334</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155826</t>
+          <t>155905</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168373</t>
+          <t>168774</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21180</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>406953</t>
+          <t>407116</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>423916</t>
+          <t>424276</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>455857</t>
+          <t>456268</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>472361</t>
+          <t>472930</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>869129</t>
+          <t>869078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>893173</t>
+          <t>892438</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22797</t>
+          <t>22437</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39760</t>
+          <t>39597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>20439</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37512</t>
+          <t>37101</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46909</t>
+          <t>47644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70953</t>
+          <t>71004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121661</t>
+          <t>121967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139461</t>
+          <t>139919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>126925</t>
+          <t>126814</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>144212</t>
+          <t>144195</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>255213</t>
+          <t>255031</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279900</t>
+          <t>279307</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26263</t>
+          <t>25805</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44063</t>
+          <t>43757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25940</t>
+          <t>25957</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43227</t>
+          <t>43338</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55976</t>
+          <t>56569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80663</t>
+          <t>80845</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>616173</t>
+          <t>616498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>643538</t>
+          <t>642454</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>668039</t>
+          <t>667625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>694179</t>
+          <t>693332</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1292618</t>
+          <t>1294693</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1330186</t>
+          <t>1330761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60499</t>
+          <t>61583</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87864</t>
+          <t>87539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54748</t>
+          <t>55595</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80888</t>
+          <t>81302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122778</t>
+          <t>122203</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>160346</t>
+          <t>158271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53211</t>
+          <t>52805</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58614</t>
+          <t>58819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60888</t>
+          <t>60179</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67266</t>
+          <t>67238</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116969</t>
+          <t>116432</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124946</t>
+          <t>125012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>430729</t>
+          <t>430845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>447937</t>
+          <t>447870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>448866</t>
+          <t>448617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>465104</t>
+          <t>464821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>885873</t>
+          <t>884998</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>908126</t>
+          <t>908870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20343</t>
+          <t>20410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37551</t>
+          <t>37435</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33696</t>
+          <t>33945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42716</t>
+          <t>41972</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64969</t>
+          <t>65844</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131924</t>
+          <t>132113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148284</t>
+          <t>148622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>147972</t>
+          <t>149696</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164382</t>
+          <t>165283</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>285667</t>
+          <t>286114</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>308748</t>
+          <t>309425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,16%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23950</t>
+          <t>23612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40310</t>
+          <t>40121</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22525</t>
+          <t>21624</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38935</t>
+          <t>37211</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50393</t>
+          <t>49716</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73474</t>
+          <t>73027</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>624673</t>
+          <t>626864</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>649068</t>
+          <t>649469</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>668091</t>
+          <t>668554</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>692183</t>
+          <t>691154</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1300595</t>
+          <t>1297779</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1333907</t>
+          <t>1333413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50824</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75219</t>
+          <t>73028</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45900</t>
+          <t>46929</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69992</t>
+          <t>69529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>104068</t>
+          <t>104562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>137380</t>
+          <t>140196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04F-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP04F-Estudios-trans_orig.xlsx
@@ -542,7 +542,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -553,7 +553,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -721,72 +721,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>80451</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>74699</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>83431</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>87,46%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>82863</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>77284</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>86769</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>76565</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>87082</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>90,46%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>80451</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>75338</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>83334</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155905</t>
+          <t>156172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168774</t>
+          <t>168634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -834,72 +834,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4954</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10706</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12,54%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8738</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4832</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14317</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4519</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15036</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>9,54%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,63%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4954</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2071</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10067</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>20834</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -947,57 +947,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85405</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85405</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85405</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91601</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91601</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91601</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>85405</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>85405</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>85405</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1064,72 +1064,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>464952</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>455075</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>471882</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>94,24%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>95,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>602</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>416424</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>407116</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>424276</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>407919</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>424208</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>93,22%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>91,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>94,98%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>464952</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>456268</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>472930</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>94,24%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>869078</t>
+          <t>868209</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>892438</t>
+          <t>891629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -1177,72 +1177,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28417</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21487</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38294</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>30289</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>22437</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39597</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>22505</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>38794</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>6,78%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>28417</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>20439</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>37101</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47644</t>
+          <t>48453</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71004</t>
+          <t>71873</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -1290,57 +1290,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>493369</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>493369</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>493369</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>648</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>446713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>446713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>446713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>493369</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>493369</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>493369</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1407,72 +1407,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>136289</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>127168</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>144650</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>80,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>74,74%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>85,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>131622</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>121967</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>139919</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>122272</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>139491</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>79,42%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>73,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>136289</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>126814</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>144195</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>80,1%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>255031</t>
+          <t>254363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279307</t>
+          <t>279539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -1520,72 +1520,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33863</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25502</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>42984</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>19,9%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>25,26%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>34102</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25805</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>43757</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>26233</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>43452</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>20,58%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>26,4%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33863</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>25957</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>43338</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>19,9%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56569</t>
+          <t>56337</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80845</t>
+          <t>81513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -1633,57 +1633,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>170152</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>170152</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>170152</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165724</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165724</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165724</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>170152</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>170152</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>170152</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1750,72 +1750,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>681692</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>668712</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>693688</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>91,02%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>89,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>92,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>911</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>630907</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>616498</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>642454</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>617404</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>643024</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>89,61%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>681692</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>667625</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>693332</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>91,02%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1294693</t>
+          <t>1291415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1330761</t>
+          <t>1329861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -1863,72 +1863,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>67235</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>55239</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>80215</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>73130</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>61583</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>87539</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>61013</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>86633</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>10,39%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>67235</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>55595</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>81302</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122203</t>
+          <t>123103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>158271</t>
+          <t>161549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -1976,57 +1976,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>748927</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>748927</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>748927</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704037</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704037</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704037</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>748927</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>748927</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>748927</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2156,7 +2156,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2324,72 +2324,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>65033</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>61061</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>67276</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>94,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>88,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>56707</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>52805</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>58819</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>52894</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>58631</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>95,5%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>88,93%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>65033</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>60179</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>67238</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>94,78%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116432</t>
+          <t>116312</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125012</t>
+          <t>125030</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -2437,72 +2437,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3581</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7553</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2671</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6573</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6484</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>4,5%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3581</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1376</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>8435</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>11681</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -2550,57 +2550,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2667,72 +2667,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>457956</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>448325</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>465372</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>94,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>664</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>440147</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>430845</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>447870</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>430647</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>447293</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>93,99%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>92,01%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>457956</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>448617</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>464821</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>94,9%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>884998</t>
+          <t>885271</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>908870</t>
+          <t>908275</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24606</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17190</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>34237</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>28133</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20410</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37435</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>20987</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>37633</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>6,01%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>24606</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>17741</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>33945</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41972</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65844</t>
+          <t>65571</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -2893,57 +2893,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>482562</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>482562</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>482562</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>707</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>468280</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>468280</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>468280</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>482562</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>482562</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>482562</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3010,72 +3010,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>157477</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>149247</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>164844</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>84,25%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>79,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>88,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>140742</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>132113</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>148622</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>131511</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>147419</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>81,72%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>76,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>157477</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>149696</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>165283</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>84,25%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>286114</t>
+          <t>286994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309425</t>
+          <t>309575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,2%</t>
         </is>
       </c>
     </row>
@@ -3123,72 +3123,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29430</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22063</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37660</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>15,75%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>31492</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23612</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>40121</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>24815</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>40723</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>18,28%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13,71%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>23,29%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>29430</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>21624</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>37211</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>15,75%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49716</t>
+          <t>49566</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73027</t>
+          <t>72147</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -3236,57 +3236,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186907</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186907</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186907</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172234</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172234</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172234</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186907</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186907</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186907</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3353,72 +3353,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>970</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>680466</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>667569</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>690857</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>92,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>90,45%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>93,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>959</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>637596</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>626864</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>649469</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>623377</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>647722</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>91,1%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>89,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>970</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>680466</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>668554</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>691154</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>92,19%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1297779</t>
+          <t>1298023</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1333413</t>
+          <t>1334574</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>47226</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>70514</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>62296</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>50423</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>73028</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>52170</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>76515</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>8,9%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>57617</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>46929</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>69529</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>104562</t>
+          <t>103401</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140196</t>
+          <t>139952</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -3579,57 +3579,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>738083</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>738083</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>738083</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1053</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>699892</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>699892</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>699892</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>738083</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>738083</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>738083</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
